--- a/data/trans_orig/Q5410-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5410-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la caca (incontinencia) en 2007</t>
+          <t>Población según si se le escapa la caca (incontinencia) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4227</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12336</t>
+          <t>13192</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14046</t>
+          <t>13884</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12786</t>
+          <t>12646</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10491</t>
+          <t>10706</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28669</t>
+          <t>28611</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15058</t>
+          <t>14685</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36015</t>
+          <t>34839</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>358753</t>
+          <t>359826</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>369654</t>
+          <t>369715</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>552647</t>
+          <t>552704</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>572765</t>
+          <t>572585</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>917553</t>
+          <t>917897</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>941000</t>
+          <t>941039</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1189,97 +1189,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1875</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5762</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>9,26%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>5663</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>6655</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>6801</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,62 +1337,62 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1952</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>4009</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>810</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>4591</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83994</t>
+          <t>83871</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56549</t>
+          <t>56450</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>142941</t>
+          <t>143379</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1645,97 +1645,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1758,97 +1758,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39010</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41194</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25052</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66007</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68075</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2393</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12911</t>
+          <t>13923</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>3212</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15554</t>
+          <t>14852</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14061</t>
+          <t>13266</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10033</t>
+          <t>10744</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28200</t>
+          <t>29772</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16563</t>
+          <t>16014</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37368</t>
+          <t>36342</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>486727</t>
+          <t>488130</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>498058</t>
+          <t>498253</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>641032</t>
+          <t>640852</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>661291</t>
+          <t>661170</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1134200</t>
+          <t>1133421</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1156736</t>
+          <t>1157292</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la caca (incontinencia) en 2012</t>
+          <t>Población según si se le escapa la caca (incontinencia) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3041</t>
+          <t>3024</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13449</t>
+          <t>13674</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9549</t>
+          <t>9664</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26921</t>
+          <t>27276</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15156</t>
+          <t>14712</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36014</t>
+          <t>36229</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>7583</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25451</t>
+          <t>25415</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11455</t>
+          <t>11369</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28211</t>
+          <t>28892</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21479</t>
+          <t>21617</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45141</t>
+          <t>46350</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>381626</t>
+          <t>380505</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>401485</t>
+          <t>400660</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>584858</t>
+          <t>586302</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>609399</t>
+          <t>609674</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>976682</t>
+          <t>975428</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1007247</t>
+          <t>1006465</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -3244,97 +3244,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2146</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>8317</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>10,01%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>2344</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>7200</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>8417</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>8,67%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>7513</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>991</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8239</t>
+          <t>9067</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>980</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8468</t>
+          <t>8414</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>110426</t>
+          <t>109598</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>117661</t>
+          <t>117674</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75874</t>
+          <t>74757</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>189382</t>
+          <t>190016</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>199716</t>
+          <t>199675</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -3700,97 +3700,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2296</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2222</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2331</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3813,97 +3813,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2296</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2222</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2331</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24279</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26575</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20024</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22246</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>46490</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48821</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>2971</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13529</t>
+          <t>13351</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11887</t>
+          <t>11873</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31475</t>
+          <t>29647</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17189</t>
+          <t>17592</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39387</t>
+          <t>38557</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10692</t>
+          <t>9737</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29010</t>
+          <t>30164</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10650</t>
+          <t>11708</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28092</t>
+          <t>28616</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22973</t>
+          <t>25443</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49577</t>
+          <t>52459</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>522180</t>
+          <t>524191</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>543702</t>
+          <t>544707</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>687887</t>
+          <t>688643</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>712376</t>
+          <t>713551</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1219066</t>
+          <t>1218148</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1252962</t>
+          <t>1251738</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la caca (incontinencia) en 2016</t>
+          <t>Población según si se le escapa la caca (incontinencia) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>967</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8351</t>
+          <t>9065</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3598</t>
+          <t>3852</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18289</t>
+          <t>19141</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23248</t>
+          <t>24664</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6764</t>
+          <t>6910</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20109</t>
+          <t>19904</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20037</t>
+          <t>21564</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15317</t>
+          <t>15117</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34974</t>
+          <t>34365</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>329117</t>
+          <t>328989</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>344176</t>
+          <t>344257</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>522440</t>
+          <t>521236</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>542793</t>
+          <t>541763</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>856989</t>
+          <t>857620</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>882589</t>
+          <t>881754</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>6406</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,62 +5334,62 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1804</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2283</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>6418</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1804</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>5978</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -5412,97 +5412,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1012</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1866</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5469</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>1012</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>4830</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>5499</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1012</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>4475</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>187015</t>
+          <t>186126</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>183244</t>
+          <t>182605</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>373106</t>
+          <t>372174</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>379715</t>
+          <t>379712</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5755,97 +5755,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1912</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5868,97 +5868,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1376</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1912</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6446</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4,09%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>19,14%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1376</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6650</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>6964</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>19,75%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1376</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>6917</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40117</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42029</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27024</t>
+          <t>27228</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>68786</t>
+          <t>68739</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11002</t>
+          <t>11822</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3819</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18360</t>
+          <t>19180</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8163</t>
+          <t>7712</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24263</t>
+          <t>24780</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6827</t>
+          <t>7140</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19897</t>
+          <t>19936</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7424</t>
+          <t>7863</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23141</t>
+          <t>24423</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17162</t>
+          <t>18043</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37180</t>
+          <t>39311</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561776</t>
+          <t>561352</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>577355</t>
+          <t>577026</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,49 +6452,49 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>98,06%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>752955</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>740202</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>761809</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>96,97%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>95,32%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
           <t>98,11%</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>635</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>752955</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>741817</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>762549</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>96,97%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>95,53%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>98,2%</t>
-        </is>
-      </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>1239</t>
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1309983</t>
+          <t>1307334</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1334530</t>
+          <t>1334803</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la caca (incontinencia) en 2023</t>
+          <t>Población según si se le escapa la caca (incontinencia) en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>992</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>6240</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>6853</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18185</t>
+          <t>17721</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9264</t>
+          <t>8954</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21372</t>
+          <t>20949</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7275</t>
+          <t>6876</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16296</t>
+          <t>16627</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30329</t>
+          <t>30299</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19669</t>
+          <t>19829</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33905</t>
+          <t>34439</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>257634</t>
+          <t>258182</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>265282</t>
+          <t>265559</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>457130</t>
+          <t>458046</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>474236</t>
+          <t>473813</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>719074</t>
+          <t>717688</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>737030</t>
+          <t>736479</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,79%</t>
         </is>
       </c>
     </row>
@@ -7354,97 +7354,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1229</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2463</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>442</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2417</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>2564</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>442</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>2471</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13374</t>
+          <t>14152</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2306</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17498</t>
+          <t>17306</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6680</t>
+          <t>6761</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>26344</t>
+          <t>25576</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>259883</t>
+          <t>259105</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>268833</t>
+          <t>268659</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>437005</t>
+          <t>437620</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>453278</t>
+          <t>453393</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>702053</t>
+          <t>702876</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>722062</t>
+          <t>722069</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,7 +7665,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -7810,97 +7810,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1192</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7923,97 +7923,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1192</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2897</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>579</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3038</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3087</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>4,26%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>579</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3482</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>103794</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>68287</t>
+          <t>68428</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>172829</t>
+          <t>173224</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>982</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6646</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5582</t>
+          <t>5229</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19315</t>
+          <t>18900</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8514</t>
+          <t>8535</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21801</t>
+          <t>21782</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7141</t>
+          <t>6979</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17904</t>
+          <t>17587</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16377</t>
+          <t>15855</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42616</t>
+          <t>43342</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27843</t>
+          <t>28301</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>56231</t>
+          <t>55522</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>625633</t>
+          <t>625982</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>637080</t>
+          <t>637610</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>969924</t>
+          <t>969036</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1005286</t>
+          <t>1006959</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1602369</t>
+          <t>1601852</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1637695</t>
+          <t>1636507</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5410-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5410-Estudios-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4231</t>
+          <t>4213</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13192</t>
+          <t>12434</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13884</t>
+          <t>13693</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12646</t>
+          <t>12464</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10706</t>
+          <t>10049</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28611</t>
+          <t>28512</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14685</t>
+          <t>16150</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34839</t>
+          <t>37379</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>359826</t>
+          <t>359854</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>369715</t>
+          <t>369863</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>552704</t>
+          <t>551871</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>572585</t>
+          <t>573533</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>917897</t>
+          <t>916009</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>941039</t>
+          <t>940031</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5762</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6655</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>4154</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83871</t>
+          <t>83918</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56450</t>
+          <t>56267</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>143379</t>
+          <t>143071</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13923</t>
+          <t>14012</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3193</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14852</t>
+          <t>15509</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3522</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13266</t>
+          <t>13962</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10744</t>
+          <t>10270</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29772</t>
+          <t>28165</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16014</t>
+          <t>17047</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36342</t>
+          <t>37699</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>488130</t>
+          <t>487510</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>498253</t>
+          <t>498172</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>640852</t>
+          <t>639905</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>661170</t>
+          <t>661311</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1133421</t>
+          <t>1133097</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1157292</t>
+          <t>1156210</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3024</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13674</t>
+          <t>13403</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>9587</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27276</t>
+          <t>26524</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,47 +2838,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,18%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>24338</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>15914</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>35739</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>1,52%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,3%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>24338</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>14712</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>36229</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7583</t>
+          <t>7651</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25415</t>
+          <t>25375</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11369</t>
+          <t>10528</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28892</t>
+          <t>27770</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21617</t>
+          <t>22596</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46350</t>
+          <t>47410</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>380505</t>
+          <t>380904</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>400660</t>
+          <t>401273</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>586302</t>
+          <t>586652</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>609674</t>
+          <t>610444</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>975428</t>
+          <t>973937</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1006465</t>
+          <t>1005680</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,88%</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8317</t>
+          <t>9123</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8417</t>
+          <t>9231</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>967</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9067</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>995</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8414</t>
+          <t>9325</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>109598</t>
+          <t>110307</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>117674</t>
+          <t>117698</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74757</t>
+          <t>73951</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>190016</t>
+          <t>189380</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>199675</t>
+          <t>199700</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13351</t>
+          <t>14414</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11873</t>
+          <t>11885</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29647</t>
+          <t>30244</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17592</t>
+          <t>17166</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38557</t>
+          <t>38646</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9737</t>
+          <t>9767</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30164</t>
+          <t>28986</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11708</t>
+          <t>11413</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28616</t>
+          <t>28435</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25443</t>
+          <t>24392</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52459</t>
+          <t>51016</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>524191</t>
+          <t>522665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>544707</t>
+          <t>543920</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>688643</t>
+          <t>688803</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>713551</t>
+          <t>713271</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1218148</t>
+          <t>1219063</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1251738</t>
+          <t>1252227</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>944</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9065</t>
+          <t>8743</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19141</t>
+          <t>20073</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>6812</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24664</t>
+          <t>22950</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6910</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19904</t>
+          <t>19586</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>6543</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21564</t>
+          <t>21435</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15117</t>
+          <t>16252</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34365</t>
+          <t>35811</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>328989</t>
+          <t>329500</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>344257</t>
+          <t>344430</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>521236</t>
+          <t>520053</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>541763</t>
+          <t>541625</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>857620</t>
+          <t>857287</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>881754</t>
+          <t>882455</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6406</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5499</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>186126</t>
+          <t>186147</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>182605</t>
+          <t>183007</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>372174</t>
+          <t>372466</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>379712</t>
+          <t>379719</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>8506</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27228</t>
+          <t>26809</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>68739</t>
+          <t>67197</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>1849</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11822</t>
+          <t>11736</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19180</t>
+          <t>19647</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>8406</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24780</t>
+          <t>25811</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>6878</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19936</t>
+          <t>19772</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7863</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24423</t>
+          <t>24153</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18043</t>
+          <t>17033</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39311</t>
+          <t>38559</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561352</t>
+          <t>562108</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>577026</t>
+          <t>577144</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>740202</t>
+          <t>739538</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761809</t>
+          <t>762072</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1307334</t>
+          <t>1308080</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1334803</t>
+          <t>1336034</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -6893,32 +6893,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2735</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6240</t>
+          <t>5754</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6928,32 +6928,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11216</t>
+          <t>12640</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6853</t>
+          <t>7582</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17721</t>
+          <t>21018</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>13951</t>
+          <t>15332</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8954</t>
+          <t>9774</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20949</t>
+          <t>23715</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -7006,32 +7006,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>3613</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>1564</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6876</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7041,32 +7041,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22772</t>
+          <t>25522</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16627</t>
+          <t>18307</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30299</t>
+          <t>33576</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>26173</t>
+          <t>29134</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19829</t>
+          <t>22106</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34439</t>
+          <t>39150</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>262504</t>
+          <t>283138</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>258182</t>
+          <t>278461</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>265559</t>
+          <t>285963</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>466247</t>
+          <t>500015</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>458046</t>
+          <t>489553</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>473813</t>
+          <t>508859</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>728751</t>
+          <t>783154</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>717688</t>
+          <t>770131</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>736479</t>
+          <t>792274</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,73%</t>
         </is>
       </c>
     </row>
@@ -7232,17 +7232,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>268639</t>
+          <t>289442</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>268639</t>
+          <t>289442</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>268639</t>
+          <t>289442</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7267,17 +7267,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>500236</t>
+          <t>538177</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>500236</t>
+          <t>538177</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>500236</t>
+          <t>538177</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>768875</t>
+          <t>827620</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>768875</t>
+          <t>827620</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>768875</t>
+          <t>827620</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>457</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2463</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>457</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>2775</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -7462,32 +7462,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>9073</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4598</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14152</t>
+          <t>14996</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7497,32 +7497,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>8625</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>5202</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17306</t>
+          <t>13259</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>16434</t>
+          <t>17698</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6761</t>
+          <t>12571</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>25576</t>
+          <t>25386</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>264910</t>
+          <t>294752</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>259105</t>
+          <t>288829</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>268659</t>
+          <t>298644</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>447211</t>
+          <t>268564</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>437620</t>
+          <t>263893</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>453393</t>
+          <t>271924</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>712121</t>
+          <t>563316</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>702876</t>
+          <t>555865</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>722069</t>
+          <t>568740</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -7688,17 +7688,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7723,17 +7723,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>652</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -7963,12 +7963,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>652</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -7998,12 +7998,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3087</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -8066,27 +8066,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>70746</t>
+          <t>82203</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>68428</t>
+          <t>79613</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8101,27 +8101,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>175732</t>
+          <t>201084</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>173224</t>
+          <t>198434</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8144,17 +8144,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2735</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>944</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>5583</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11658</t>
+          <t>13097</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5229</t>
+          <t>8075</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18900</t>
+          <t>21783</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>14393</t>
+          <t>15789</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8535</t>
+          <t>10335</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21782</t>
+          <t>24173</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -8374,32 +8374,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11748</t>
+          <t>12685</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6979</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17587</t>
+          <t>19147</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8409,32 +8409,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>31438</t>
+          <t>34799</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15855</t>
+          <t>26659</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43342</t>
+          <t>43404</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>43186</t>
+          <t>47485</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28301</t>
+          <t>38004</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55522</t>
+          <t>59509</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -8487,32 +8487,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>632399</t>
+          <t>696772</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>625982</t>
+          <t>689462</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>637610</t>
+          <t>702413</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8522,32 +8522,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>984204</t>
+          <t>850781</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>969036</t>
+          <t>838883</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1006959</t>
+          <t>860510</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1616602</t>
+          <t>1547553</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1601852</t>
+          <t>1533912</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1636507</t>
+          <t>1559681</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -8600,17 +8600,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>646882</t>
+          <t>712149</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>646882</t>
+          <t>712149</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>646882</t>
+          <t>712149</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8635,17 +8635,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1027300</t>
+          <t>898678</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1027300</t>
+          <t>898678</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1027300</t>
+          <t>898678</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1674181</t>
+          <t>1610827</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1674181</t>
+          <t>1610827</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1674181</t>
+          <t>1610827</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
